--- a/stories/arbres/ATOM-EMO.LEX.007-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules est à l'école. Il attend son tour pour parler. La maîtresse parle encore. Jules sent ses jambes bouger. Son corps ne tient pas en place. Jules dit : je suis nerveux. Il lève la main. Il dit : je demande une pause. La maîtresse dit : oui, Jules. Jules s'assoit sur le banc près de la fenêtre. Il pose les pieds au sol. Il souffle. Ses jambes se calment. Plus tard, maman vient le chercher. Jules dit : j'étais nerveux. J'ai demandé une pause. Maman dit : ton corps a parlé. On peut faire une pause.</t>
+          <t>Jules est à l'école. Il attend son tour pour parler. La maîtresse parle encore. Jules sent ses jambes bouger. Son corps ne tient pas en place. Je suis nerveux. Il lève la main. Je demande une pause. Oui, Jules. Jules s'assoit sur le banc près de la fenêtre. Il pose les pieds au sol. Il souffle. Ses jambes se calment. Plus tard, maman vient le chercher. J'étais nerveux. J'ai demandé une pause. Ton corps a parlé. On peut faire une pause.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Jules est à l'école. Il attend son tour pour parler. La maîtresse parle encore. Jules sent ses jambes bouger. Son corps ne tient pas en place.
+enfant-m|Je suis nerveux. Il lève la main.
+narrateur|Je demande une pause.
+maitresse|Oui, Jules.
+narrateur|Jules s'assoit sur le banc près de la fenêtre. Il pose les pieds au sol. Il souffle. Ses jambes se calment. Plus tard, maman vient le chercher.
+enfant-m|J'étais nerveux. J'ai demandé une pause.
+maman|Ton corps a parlé. On peut faire une pause.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Jules ne tient plus. Que demande-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a nommé : nerveux. Il a demandé une pause. Il s'est assis. Ce n'est pas une faute.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Jules prend la main de maman. Le chemin de l'école est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.007-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 maman|Ton corps a parlé. On peut faire une pause.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Jules ne tient plus. Que demande-t-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Jules a nommé : nerveux. Il a demandé une pause. Il s'est assis. Ce n'est pas une faute.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Jules prend la main de maman. Le chemin de l'école est calme.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.007-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Être nerveux</t>
+          <t>Raphaël demande une pause</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Dans le couloir, Raphaël attend. Ses jambes bougent. Il nomme nerveux. Il demande une pause et s'assoit.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules est à l'école. Il attend son tour pour parler. La maîtresse parle encore. Jules sent ses jambes bouger. Son corps ne tient pas en place. Je suis nerveux. Il lève la main. Je demande une pause. Oui, Jules. Jules s'assoit sur le banc près de la fenêtre. Il pose les pieds au sol. Il souffle. Ses jambes se calment. Plus tard, maman vient le chercher. J'étais nerveux. J'ai demandé une pause. Ton corps a parlé. On peut faire une pause.</t>
+          <t>Les patères cliquent dans le couloir. Un manteau bleu balance un peu. Ça sent la craie, tout doux. Le cartable de Raphaël est bleu aussi. La cour est encore un peu humide. Une feuille collée brille près de la porte. On attend ici un moment, Raphaël. Le manteau balance. Oui. Il sèche un peu. Le banc près de la fenêtre est lisse. Le bois est froid sous la main. Tu as vu la feuille collée ? Elle brille. La cour l'a mouillée. En ce moment, Raphaël attend avec maman. Ils sont dans le couloir de l'école. Une voix parle encore, derrière une porte. Raphaël attend son tour pour parler. Ses jambes bougent. Ses pieds tapent tout bas le sol. Son corps ne tient pas en place. Je suis nerveux. Mes jambes bougent. Ton corps parle. On peut demander une pause. Je demande une pause. Oui, Raphaël. On s'assoit. Raphaël s'assoit sur le banc près de la fenêtre. Il pose les pieds au sol. Les pieds sont posés. Tu souffles avec moi ? Oui, maman. Raphaël souffle. Ses jambes se calment un peu. Nerveux, ce n'est pas vilain. Une pause, c'est bien. Bravo, Raphaël. C'est du bon travail. Tu as demandé la pause ? Oui. Je suis nerveux. Tu as nommé. Tu t'es assis. La voix derrière la porte s'arrête. Le manteau bleu ne balance plus. On peut parler, maintenant ? Un peu. Mes pieds sont au sol. Oui. Ils sont bien posés. Plus tard, ils prennent le chemin. La cour a séché un peu. J'étais nerveux. J'ai demandé une pause. Ton corps a parlé. On peut faire une pause. Tu as les jambes plus calmes ? Oui, maman. La feuille collée reste près de la porte. Elle brille moins. On rentre, tout doux. La main dans ta main. Oui.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,78 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Jules est à l'école. Il attend son tour pour parler. La maîtresse parle encore. Jules sent ses jambes bouger. Son corps ne tient pas en place.
-enfant-m|Je suis nerveux. Il lève la main.
-narrateur|Je demande une pause.
-maitresse|Oui, Jules.
-narrateur|Jules s'assoit sur le banc près de la fenêtre. Il pose les pieds au sol. Il souffle. Ses jambes se calment. Plus tard, maman vient le chercher.
-enfant-m|J'étais nerveux. J'ai demandé une pause.
-maman|Ton corps a parlé. On peut faire une pause.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Les patères cliquent dans le couloir.
+narrateur|Un manteau bleu balance un peu.
+narrateur|Ça sent la craie, tout doux.
+narrateur|Le cartable de Raphaël est bleu aussi.
+narrateur|La cour est encore un peu humide.
+narrateur|Une feuille collée brille près de la porte.
+maman|On attend ici un moment, Raphaël.
+enfant-m|Le manteau balance.
+maman|Oui.
+maman|Il sèche un peu.
+narrateur|Le banc près de la fenêtre est lisse.
+narrateur|Le bois est froid sous la main.
+maman|Tu as vu la feuille collée ?
+enfant-m|Elle brille.
+maman|La cour l'a mouillée.
+narrateur|En ce moment, Raphaël attend avec maman.
+narrateur|Ils sont dans le couloir de l'école.
+narrateur|Une voix parle encore, derrière une porte.
+narrateur|Raphaël attend son tour pour parler.
+narrateur|Ses jambes bougent.
+narrateur|Ses pieds tapent tout bas le sol.
+narrateur|Son corps ne tient pas en place.
+enfant-m|Je suis nerveux.
+enfant-m|Mes jambes bougent.
+maman|Ton corps parle.
+maman|On peut demander une pause.
+enfant-m|Je demande une pause.
+maman|Oui, Raphaël.
+maman|On s'assoit.
+narrateur|Raphaël s'assoit sur le banc près de la fenêtre.
+narrateur|Il pose les pieds au sol.
+maman|Les pieds sont posés.
+maman|Tu souffles avec moi ?
+enfant-m|Oui, maman.
+narrateur|Raphaël souffle.
+narrateur|Ses jambes se calment un peu.
+maman|Nerveux, ce n'est pas vilain.
+maman|Une pause, c'est bien.
+maman|Bravo, Raphaël.
+maman|C'est du bon travail.
+maman|Tu as demandé la pause ?
+enfant-m|Oui.
+enfant-m|Je suis nerveux.
+maman|Tu as nommé.
+maman|Tu t'es assis.
+narrateur|La voix derrière la porte s'arrête.
+narrateur|Le manteau bleu ne balance plus.
+maman|On peut parler, maintenant ?
+enfant-m|Un peu.
+enfant-m|Mes pieds sont au sol.
+maman|Oui.
+maman|Ils sont bien posés.
+narrateur|Plus tard, ils prennent le chemin.
+narrateur|La cour a séché un peu.
+enfant-m|J'étais nerveux.
+enfant-m|J'ai demandé une pause.
+maman|Ton corps a parlé.
+maman|On peut faire une pause.
+maman|Tu as les jambes plus calmes ?
+enfant-m|Oui, maman.
+narrateur|La feuille collée reste près de la porte.
+narrateur|Elle brille moins.
+maman|On rentre, tout doux.
+enfant-m|La main dans ta main.
+maman|Oui.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>couloir_ecole</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1420,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Jules ne tient plus. Que demande-t-il ?</t>
+          <t>Raphaël ne tient plus. Que demande-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1576,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Jules ne tient plus. Que demande-t-il ?</t>
+          <t>narrateur|Raphaël ne tient plus.
+narrateur|Que demande-t-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1605,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules a nommé : nerveux. Il a demandé une pause. Il s'est assis. Ce n'est pas une faute.</t>
+          <t>Raphaël a nommé : nerveux. Il a demandé une pause. Il s'est assis. Ce n'est pas une faute. Bravo, Raphaël. Tu as demandé une pause. C'est du bon travail. Je suis nerveux. J'ai demandé une pause. Oui. Tu t'es assis. Les pieds au sol ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1749,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Jules a nommé : nerveux. Il a demandé une pause. Il s'est assis. Ce n'est pas une faute.</t>
+          <t>narrateur|Raphaël a nommé : nerveux.
+narrateur|Il a demandé une pause.
+narrateur|Il s'est assis.
+narrateur|Ce n'est pas une faute.
+maman|Bravo, Raphaël.
+maman|Tu as demandé une pause.
+maman|C'est du bon travail.
+enfant-m|Je suis nerveux.
+enfant-m|J'ai demandé une pause.
+maman|Oui.
+maman|Tu t'es assis.
+maman|Les pieds au sol ?
+enfant-m|Oui, maman.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1789,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Jules prend la main de maman. Le chemin de l'école est calme.</t>
+          <t>Raphaël prend la main de maman. Le chemin de l'école est calme. On marche tout doux ? Oui. Mes jambes sont calmes. La pause a aidé. Le cartable bleu tape un peu la hanche. Ça sent encore un peu la craie. Tu restes près de moi ? Oui, maman. Une flaque reflète le ciel pâle. Ils la contournent ensemble.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1929,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Jules prend la main de maman. Le chemin de l'école est calme.</t>
+          <t>narrateur|Raphaël prend la main de maman.
+narrateur|Le chemin de l'école est calme.
+maman|On marche tout doux ?
+enfant-m|Oui.
+enfant-m|Mes jambes sont calmes.
+maman|La pause a aidé.
+narrateur|Le cartable bleu tape un peu la hanche.
+narrateur|Ça sent encore un peu la craie.
+maman|Tu restes près de moi ?
+enfant-m|Oui, maman.
+narrateur|Une flaque reflète le ciel pâle.
+narrateur|Ils la contournent ensemble.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1968,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai demandé une pause. J'étais nerveux. Bravo. Tu as fait du bon travail. Le manteau bleu sèche encore, loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2108,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai demandé une pause.
+enfant-m|J'étais nerveux.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le manteau bleu sèche encore, loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2173,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.007-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les patères cliquent dans le couloir. Un manteau bleu balance un peu. Ça sent la craie, tout doux. Le cartable de Raphaël est bleu aussi. La cour est encore un peu humide. Une feuille collée brille près de la porte. On attend ici un moment, Raphaël. Le manteau balance. Oui. Il sèche un peu. Le banc près de la fenêtre est lisse. Le bois est froid sous la main. Tu as vu la feuille collée ? Elle brille. La cour l'a mouillée. En ce moment, Raphaël attend avec maman. Ils sont dans le couloir de l'école. Une voix parle encore, derrière une porte. Raphaël attend son tour pour parler. Ses jambes bougent. Ses pieds tapent tout bas le sol. Son corps ne tient pas en place. Je suis nerveux. Mes jambes bougent. Ton corps parle. On peut demander une pause. Je demande une pause. Oui, Raphaël. On s'assoit. Raphaël s'assoit sur le banc près de la fenêtre. Il pose les pieds au sol. Les pieds sont posés. Tu souffles avec moi ? Oui, maman. Raphaël souffle. Ses jambes se calment un peu. Nerveux, ce n'est pas vilain. Une pause, c'est bien. Bravo, Raphaël. C'est du bon travail. Tu as demandé la pause ? Oui. Je suis nerveux. Tu as nommé. Tu t'es assis. La voix derrière la porte s'arrête. Le manteau bleu ne balance plus. On peut parler, maintenant ? Un peu. Mes pieds sont au sol. Oui. Ils sont bien posés. Plus tard, ils prennent le chemin. La cour a séché un peu. J'étais nerveux. J'ai demandé une pause. Ton corps a parlé. On peut faire une pause. Tu as les jambes plus calmes ? Oui, maman. La feuille collée reste près de la porte. Elle brille moins. On rentre, tout doux. La main dans ta main. Oui.</t>
+          <t>Les patères cliquent dans le couloir. Un manteau bleu balance un peu. Ça sent la craie, tout doux. Le cartable de Raphaël est bleu aussi. La cour est encore un peu humide. Une feuille collée brille près de la porte. On attend ici un moment, Raphaël. Le manteau balance. Oui. Il sèche un peu. Le banc près de la fenêtre est lisse. Le bois est froid sous la main. Tu as vu la feuille collée ? Elle brille. La cour l'a mouillée. En ce moment, Raphaël attend avec maman. Ils sont dans le couloir de l'école. Une voix parle encore, derrière une porte. Raphaël attend son tour pour parler. Ses jambes bougent. Ses pieds tapent tout bas le sol. Son corps ne tient pas en place. Je suis nerveux. Mes jambes bougent. Ton corps parle. On peut demander une pause. Je demande une pause. Oui, Raphaël. On s'assoit. Raphaël s'assoit sur le banc près de la fenêtre. Il pose les pieds au sol. Les pieds sont posés. Tu souffles avec moi ? Oui, maman. Raphaël souffle. Ses jambes se calment un peu. Nerveux, ce n'est pas vilain. Une pause, c'est bien. Bravo, Raphaël. Tu as demandé la pause ? Oui. Je suis nerveux. Tu as nommé. Tu t'es assis. La voix derrière la porte s'arrête. Le manteau bleu ne balance plus. On peut parler, maintenant ? Un peu. Mes pieds sont au sol. Oui. Ils sont bien posés. Plus tard, ils prennent le chemin. La cour a séché un peu. J'étais nerveux. J'ai demandé une pause. Ton corps a parlé. On peut faire une pause. Tu as les jambes plus calmes ? Oui, maman. La feuille collée reste près de la porte. Elle brille moins. On rentre, tout doux. La main dans ta main. Oui.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jules est à l'école. Il attend son tour pour parler. La maîtresse parle encore. Jules sent ses jambes bouger. Son corps ne tient pas en place. Jules dit : je suis &lt;emphasis level="moderate"&gt;nerveux&lt;/emphasis&gt;. Il lève la main. Il dit : je demande une pause. La maîtresse dit : oui, Jules. Jules s'assoit sur le banc près de la fenêtre. Il pose les pieds au sol. Il souffle. Ses jambes se calment. Plus tard, maman vient le chercher. Jules dit : j'étais nerveux. J'ai demandé une pause. Maman dit : ton corps a parlé. On peut faire une pause.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les patères cliquent dans le couloir. Un manteau bleu balance un peu. Ça sent la craie, tout doux. Le cartable de Raphaël est bleu aussi. La cour est encore un peu humide. Une feuille collée brille près de la porte. On attend ici un moment, Raphaël. Le manteau balance. Oui. Il sèche un peu. Le banc près de la fenêtre est lisse. Le bois est froid sous la main. Tu as vu la feuille collée ? Elle brille. La cour l'a mouillée. En ce moment, Raphaël attend avec maman. Ils sont dans le couloir de l'école. Une voix parle encore, derrière une porte. Raphaël attend son tour pour parler. Ses jambes bougent. Ses pieds tapent tout bas le sol. Son corps ne tient pas en place. Je suis nerveux. Mes jambes bougent. Ton corps parle. On peut demander une pause. Je demande une pause. Oui, Raphaël. On s'assoit. Raphaël s'assoit sur le banc près de la fenêtre. Il pose les pieds au sol. Les pieds sont posés. Tu souffles avec moi ? Oui, maman. Raphaël souffle. Ses jambes se calment un peu. Nerveux, ce n'est pas vilain. Une pause, c'est bien. Bravo, Raphaël. Tu as demandé la pause ? Oui. Je suis nerveux. Tu as nommé. Tu t'es assis. La voix derrière la porte s'arrête. Le manteau bleu ne balance plus. On peut parler, maintenant ? Un peu. Mes pieds sont au sol. Oui. Ils sont bien posés. Plus tard, ils prennent le chemin. La cour a séché un peu. J'étais nerveux. J'ai demandé une pause. Ton corps a parlé. On peut faire une pause. Tu as les jambes plus calmes ? Oui, maman. La feuille collée reste près de la porte. Elle brille moins. On rentre, tout doux. La main dans ta main. Oui.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1363,7 +1363,6 @@
 maman|Nerveux, ce n'est pas vilain.
 maman|Une pause, c'est bien.
 maman|Bravo, Raphaël.
-maman|C'est du bon travail.
 maman|Tu as demandé la pause ?
 enfant-m|Oui.
 enfant-m|Je suis nerveux.
@@ -1425,7 +1424,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Jules ne tient plus. Que demande-t-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël ne tient plus. Que demande-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1580,7 +1579,6 @@
 narrateur|Que demande-t-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1605,12 +1603,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a nommé : nerveux. Il a demandé une pause. Il s'est assis. Ce n'est pas une faute. Bravo, Raphaël. Tu as demandé une pause. C'est du bon travail. Je suis nerveux. J'ai demandé une pause. Oui. Tu t'es assis. Les pieds au sol ? Oui, maman.</t>
+          <t>Raphaël a nommé : nerveux. Il a demandé une pause. Il s'est assis. Ce n'est pas une faute. Bravo, Raphaël. Tu as demandé une pause. Je suis nerveux. J'ai demandé une pause. Oui. Tu t'es assis. Les pieds au sol ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jules a nommé : &lt;emphasis level="moderate"&gt;nerveux&lt;/emphasis&gt;. Il a demandé une pause. Il s'est assis. Ce n'est pas une faute.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a nommé : nerveux. Il a demandé une pause. Il s'est assis. Ce n'est pas une faute. Bravo, Raphaël. Tu as demandé une pause. Je suis nerveux. J'ai demandé une pause. Oui. Tu t'es assis. Les pieds au sol ? Oui, maman.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1755,7 +1753,6 @@
 narrateur|Ce n'est pas une faute.
 maman|Bravo, Raphaël.
 maman|Tu as demandé une pause.
-maman|C'est du bon travail.
 enfant-m|Je suis nerveux.
 enfant-m|J'ai demandé une pause.
 maman|Oui.
@@ -1764,7 +1761,6 @@
 enfant-m|Oui, maman.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1794,7 +1790,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jules prend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de maman. Le chemin de l'école est calme.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël prend la main de maman. Le chemin de l'école est calme. On marche tout doux ? Oui. Mes jambes sont calmes. La pause a aidé. Le cartable bleu tape un peu la hanche. Ça sent encore un peu la craie. Tu restes près de moi ? Oui, maman. Une flaque reflète le ciel pâle. Ils la contournent ensemble.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1943,7 +1939,6 @@
 narrateur|Ils la contournent ensemble.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1968,12 +1963,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai demandé une pause. J'étais nerveux. Bravo. Tu as fait du bon travail. Le manteau bleu sèche encore, loin. L'histoire est finie.</t>
+          <t>J'ai demandé une pause. J'étais nerveux. Bravo. Le manteau bleu sèche encore, loin.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai demandé une pause. J'étais nerveux. Bravo. Le manteau bleu sèche encore, loin.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2111,12 +2106,9 @@
           <t>enfant-m|J'ai demandé une pause.
 enfant-m|J'étais nerveux.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le manteau bleu sèche encore, loin.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le manteau bleu sèche encore, loin.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2135,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2180,6 +2172,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.007-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-01.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jules, maman</t>
+          <t>Raphaël, maman</t>
         </is>
       </c>
     </row>
